--- a/Журнал_арендных_платежей_v3.xlsx
+++ b/Журнал_арендных_платежей_v3.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Главная" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Регистрация" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="История" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Аналитика" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Справочники" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Главная" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Регистрация" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="История" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Аналитика" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Справочники" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="RENT">Главная!$B$9</definedName>
@@ -31,7 +31,7 @@
     <definedName name="J_PER">Регистрация!$I$7:$I$306</definedName>
     <definedName name="J_SUM">Регистрация!$E$7:$E$306</definedName>
     <definedName name="J_PAY">Регистрация!$F$7:$F$306</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Главная'!$A$1:$E$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Главная'!$A$1:$E$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Регистрация'!$A$6:$I$306</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Регистрация'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Регистрация'!$A$1:$I$56</definedName>
@@ -58,7 +58,7 @@
     <numFmt numFmtId="171" formatCode="0.0%"/>
     <numFmt numFmtId="172" formatCode="0&quot; дн.&quot;"/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="35">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -155,6 +155,12 @@
     <font>
       <name val="Arial"/>
       <color rgb="007A7590"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C97C1B"/>
       <sz val="9.5"/>
     </font>
     <font>
@@ -286,6 +292,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FDF3E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="000E8F8C"/>
       </patternFill>
     </fill>
@@ -307,11 +318,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E6F6EE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDF3E2"/>
       </patternFill>
     </fill>
     <fill>
@@ -853,65 +859,65 @@
     <xf numFmtId="0" fontId="16" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="18" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="19" fillId="2" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="20" fillId="2" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="2" borderId="28" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="21" fillId="2" borderId="28" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="28" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="28" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="170" fontId="20" fillId="2" borderId="28" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="21" fillId="2" borderId="28" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="166" fontId="21" fillId="2" borderId="28" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="22" fillId="2" borderId="28" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="23" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="24" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -920,119 +926,119 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="24" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="25" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="26" fillId="2" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="27" fillId="2" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="20" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="20" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="21" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="22" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="28" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="29" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="30" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="30" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="31" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="30" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="31" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="26" fillId="2" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="27" fillId="2" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="26" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="27" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="171" fontId="0" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="19" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="20" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="171" fontId="6" fillId="2" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="172" fontId="6" fillId="2" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="4" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -1042,49 +1048,49 @@
     <xf numFmtId="1" fontId="5" fillId="2" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="4" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="4" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="4" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2061,22 +2067,26 @@
       <c r="E30" s="47" t="n"/>
     </row>
     <row r="31" ht="19" customHeight="1">
-      <c r="A31" s="48" t="inlineStr">
-        <is>
-          <t>4.  Сиреневые ячейки 🤖 — формулы. Защита без пароля: «Рецензирование → Снять защиту листа».</t>
-        </is>
-      </c>
-      <c r="B31" s="49" t="n"/>
-      <c r="C31" s="49" t="n"/>
-      <c r="D31" s="49" t="n"/>
-      <c r="E31" s="50" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="n"/>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="3" t="n"/>
-      <c r="E32" s="3" t="n"/>
+      <c r="A31" s="42" t="inlineStr">
+        <is>
+          <t>4.  Сиреневые ячейки 🤖 — формулы, их заполнять не нужно.</t>
+        </is>
+      </c>
+      <c r="B31" s="43" t="n"/>
+      <c r="C31" s="43" t="n"/>
+      <c r="D31" s="43" t="n"/>
+      <c r="E31" s="44" t="n"/>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="48" t="inlineStr">
+        <is>
+          <t>5.  Если ввод не вставляется — вверху Excel нажмите «Разрешить редактирование» (жёлтая полоса «Защищённый просмотр») и сохраните файл на компьютер.</t>
+        </is>
+      </c>
+      <c r="B32" s="49" t="n"/>
+      <c r="C32" s="49" t="n"/>
+      <c r="D32" s="49" t="n"/>
+      <c r="E32" s="50" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n"/>
@@ -2135,8 +2145,7 @@
       <c r="E40" s="3" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="0"/>
-  <mergeCells count="25">
+  <mergeCells count="26">
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="D20:E20"/>
     <mergeCell ref="A15:B15"/>
@@ -2153,6 +2162,7 @@
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B11:E11"/>
     <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A32:E32"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A29:E29"/>
@@ -2280,7 +2290,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Одна строка — один платёж. Достаточно заполнить: Дата · Категория · Сумма — месяц подставится сам из даты платежа</t>
+          <t>Одна строка — один платёж. Достаточно заполнить: Дата · Категория · Сумма — месяц подставится сам. Не вставляется значение? Нажмите «Разрешить редактирование» вверху Excel</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -8420,7 +8430,6 @@
       <c r="I308" s="3" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <autoFilter ref="A6:I306"/>
   <mergeCells count="7">
     <mergeCell ref="A4:B4"/>
@@ -8475,13 +8484,13 @@
   </conditionalFormatting>
   <dataValidations count="5">
     <dataValidation sqref="C7:C306" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Категория" error="Обычно выбирают из списка. Оставить введённое значение?" promptTitle="Категория платежа" prompt="Выберите из списка или впишите: Аренда · Налог · Коммунальные услуги · Залог · Прочее" type="list" errorStyle="warning">
-      <formula1>L_CAT</formula1>
+      <formula1>"Аренда,Налог,Коммунальные услуги,Залог,Прочее"</formula1>
     </dataValidation>
     <dataValidation sqref="D7:D306" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Месяц" error="Обычно выбирают месяц из списка. Оставить введённое значение?" promptTitle="Месяц — заполнять не обязательно" prompt="Оставьте пусто — платёж зачтётся за месяц своей даты. Заполняйте только для аванса или погашения долга за другой месяц." type="list" errorStyle="warning">
       <formula1>L_PER</formula1>
     </dataValidation>
     <dataValidation sqref="F7:F306" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Способ оплаты" error="Обычно выбирают из списка. Оставить введённое значение?" promptTitle="Способ оплаты" prompt="Выберите из списка или впишите свой вариант." type="list" errorStyle="warning">
-      <formula1>L_PAY</formula1>
+      <formula1>"Наличные,Перевод СБП,Банковская карта,Расчётный счёт,Почтовый перевод,Другое"</formula1>
     </dataValidation>
     <dataValidation sqref="E7:E306" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Сумма" error="Ожидается число больше нуля. Оставить как есть?" type="decimal" errorStyle="warning" operator="greaterThan">
       <formula1>0</formula1>
@@ -11942,7 +11951,7 @@
       <c r="C26" s="116" t="n"/>
       <c r="D26" s="117" t="inlineStr">
         <is>
-          <t>Это только образец на память — копировать ничего не нужно. Столбец «Месяц» можно не заполнять: платёж зачтётся за месяц своей даты, а колонка «🤖 Учтён за месяц» покажет результат. Значения можно выбирать из списка или вписывать вручную. Листы защищены без пароля: «Рецензирование → Снять защиту листа».</t>
+          <t>Это только образец на память — копировать ничего не нужно. Столбец «Месяц» можно не заполнять: платёж зачтётся за месяц своей даты, а колонка «🤖 Учтён за месяц» покажет результат. Значения выбираются из списка или вписываются вручную. Списки категорий и способов оплаты зашиты в проверку данных на листе «Регистрация»: чтобы изменить, выделите столбец и откройте «Данные → Проверка данных».</t>
         </is>
       </c>
       <c r="E26" s="118" t="n"/>
